--- a/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0001T0006Z000C1N12_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0001T0006Z000C1N12_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>32.66386671748691</v>
+        <v>5.307878341591623</v>
       </c>
       <c r="D2" t="n">
-        <v>23.38809710984954</v>
+        <v>3.80056578035055</v>
       </c>
       <c r="E2" t="n">
-        <v>7.585876615894263</v>
+        <v>1.232704950082818</v>
       </c>
       <c r="F2" t="n">
-        <v>3.951209301847698</v>
+        <v>0.6420715115502509</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>16.5311224429005</v>
+        <v>2.686307396971331</v>
       </c>
       <c r="D3" t="n">
-        <v>16.91828581924682</v>
+        <v>2.749221445627609</v>
       </c>
       <c r="E3" t="n">
-        <v>7.585876615894263</v>
+        <v>1.232704950082818</v>
       </c>
       <c r="F3" t="n">
-        <v>3.951209301847698</v>
+        <v>0.6420715115502509</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>21.42530345483176</v>
+        <v>3.48161181141016</v>
       </c>
       <c r="D4" t="n">
-        <v>16.91892431568863</v>
+        <v>2.749325201299403</v>
       </c>
       <c r="E4" t="n">
-        <v>7.585876615894263</v>
+        <v>1.232704950082818</v>
       </c>
       <c r="F4" t="n">
-        <v>3.951209301847698</v>
+        <v>0.6420715115502509</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>9.1241032881588</v>
+        <v>1.482666784325805</v>
       </c>
       <c r="D5" t="n">
-        <v>19.57255293330111</v>
+        <v>3.180539851661431</v>
       </c>
       <c r="E5" t="n">
-        <v>7.585876615894263</v>
+        <v>1.232704950082818</v>
       </c>
       <c r="F5" t="n">
-        <v>3.951209301847698</v>
+        <v>0.6420715115502509</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>21.23940806227698</v>
+        <v>3.451403810120009</v>
       </c>
       <c r="D6" t="n">
-        <v>21.81775256721659</v>
+        <v>3.545384792172695</v>
       </c>
       <c r="E6" t="n">
-        <v>7.585876615894263</v>
+        <v>1.232704950082818</v>
       </c>
       <c r="F6" t="n">
-        <v>3.951209301847698</v>
+        <v>0.6420715115502509</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>8.515843273686512</v>
+        <v>1.383824531974058</v>
       </c>
       <c r="D7" t="n">
-        <v>9.898817087377667</v>
+        <v>1.608557776698871</v>
       </c>
       <c r="E7" t="n">
-        <v>7.585876615894263</v>
+        <v>1.232704950082818</v>
       </c>
       <c r="F7" t="n">
-        <v>3.951209301847698</v>
+        <v>0.6420715115502509</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>16.0312195418814</v>
+        <v>2.605073175555727</v>
       </c>
       <c r="D8" t="n">
-        <v>16.57392511268479</v>
+        <v>2.693262830811279</v>
       </c>
       <c r="E8" t="n">
-        <v>7.585876615894263</v>
+        <v>1.232704950082818</v>
       </c>
       <c r="F8" t="n">
-        <v>3.951209301847698</v>
+        <v>0.6420715115502509</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>20.6423392168417</v>
+        <v>3.354380122736776</v>
       </c>
       <c r="D9" t="n">
-        <v>24.60883319464403</v>
+        <v>3.998935394129655</v>
       </c>
       <c r="E9" t="n">
-        <v>7.585876615894263</v>
+        <v>1.232704950082818</v>
       </c>
       <c r="F9" t="n">
-        <v>3.951209301847698</v>
+        <v>0.6420715115502509</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>24.55450112254837</v>
+        <v>3.99010643241411</v>
       </c>
       <c r="D10" t="n">
-        <v>18.98669096874042</v>
+        <v>3.085337282420318</v>
       </c>
       <c r="E10" t="n">
-        <v>7.585876615894263</v>
+        <v>1.232704950082818</v>
       </c>
       <c r="F10" t="n">
-        <v>3.951209301847698</v>
+        <v>0.6420715115502509</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>30.61045573002793</v>
+        <v>4.97419905612954</v>
       </c>
       <c r="D11" t="n">
-        <v>19.36865147333062</v>
+        <v>3.147405864416226</v>
       </c>
       <c r="E11" t="n">
-        <v>7.585876615894263</v>
+        <v>1.232704950082818</v>
       </c>
       <c r="F11" t="n">
-        <v>3.951209301847698</v>
+        <v>0.6420715115502509</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
